--- a/Stage_B/Decision_Log_Stage_B.xlsx
+++ b/Stage_B/Decision_Log_Stage_B.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Stage A" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Stage B" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -151,7 +151,7 @@
     <t>Replace the planned B1 ClimateBERT filter, B2 regex pillar tagger, and B3 four-way content router with a two-step hybrid: (1) ClimateBERT screens each segment for climate relevance; (2) segments passing the filter go to a single GPT-4o or Claude Sonnet call that returns structured JSON containing: tcfd_pillar (one of four TCFD labels or Other), content_type (pledge / kpi / time_series_kpi / materiality_matrix / boilerplate), and pledge_text (extracted pledge string or null).</t>
   </si>
   <si>
-    <t>Across four firms reviewed (Cathay Pacific, CR Power, ENN Energy, JD Logistics), each report introduced new structural variation: different heading formats, spread layouts, goal-progress tables with different column arrangements, garbled appendix fonts. Separate rule-based fixes (DL-009 to DL-016) were accumulating without bound. The core research contribution is the scoring schema (Stage D), not the classification machinery. Pipeline is intended to scale to n=200, at which point ClimateBERT's accuracy advantage over a pure LLM filter becomes meaningful and measurable (P9 Wang and Zhou 2026 shows ClimateBERT-class models reach 0.993 F1 on climate classification at scale).</t>
+    <t>Across four firms reviewed (Cathay Pacific, CR Power, ENN Energy, JD Logistics), each report introduced new structural variation: different heading formats, spread layouts, goal-progress tables with different column arrangements, garbled appendix fonts. Separate rule-based fixes (DL-009 to DL-016) were accumulating without bound. The core research contribution is the scoring schema (Stage D), not the classification machinery. Pipeline is intended to scale to n=200.</t>
   </si>
   <si>
     <t>(1) Continue building per-firm rules (DL-009 to DL-016 approach). (2) ClimateBERT for climate relevance plus single LLM call for pillar, content type, and pledge extraction. (3) Single LLM call for all three tasks simultaneously.</t>
@@ -163,14 +163,171 @@
     <t>ClimateBERT adds one model dependency and download; mitigated by the fact it is a standard pip-installable model already cited in P1 (Bingler et al. 2022) as the methodological anchor of this project. LLM output varies across runs; mitigated by logging model name, version, and run date, same as DL-002. Both prompts must be fixed and versioned in the replication package.</t>
   </si>
   <si>
-    <t>DL-009, DL-010, DL-013, DL-014 (Stage B routing decisions) and DL-011, DL-016 (Stage A heading-parser decisions) are all superseded by this entry. P9 (Wang and Zhou 2026) validates ClimateBERT-class accuracy at 0.993 F1 at scale. P10 (Xu and Suzuki 2026) validates GPT-4o zero-shot structured extraction at 89.5% accuracy. Estimated LLM cost at n=7: under USD 1. At n=200: still under USD 30.</t>
+    <t>CORRECTED [see DL-024]: DL-009, DL-010, DL-013, DL-014 (Stage B routing decisions) and DL-011, DL-016 (Stage A heading-parser decisions) are all superseded by this entry. P10 (Xu and Suzuki 2026) validates GPT-4o zero-shot structured extraction at 89.5% accuracy, grounding the LLM half of this decision. The prior claim that P9 (Wang and Zhou 2026) shows ClimateBERT-class models reach 0.993 F1 at scale is removed: the mastersheet P9 row is Wang and Zhou's SDG-omission/greenwashing-tone paper, which reports no such ClimateBERT F1 figure, and no correct source for that number has been located. The ClimateBERT half of this decision now rests on P1 (Bingler et al. 2022) alone, which validates ClimateBERT for TCFD-relevant sentence classification but does not itself report a 0.993 F1 figure; the specific accuracy-at-scale claim is retracted, not replaced, and DL-018's justification for keeping ClimateBERT over a pure-LLM filter is now the simpler point that a validated domain classifier is free and requires no per-run API cost, not a specific superiority number. Estimated LLM cost at n=7: under USD 1. At n=200: still under USD 30, unaffected by this correction.</t>
+  </si>
+  <si>
+    <t>The A2-priority resolution rule has a failure mode worth watching. If a metrics sentence like S1 happens to sit under a chapter A2 tagged "Strategy," the rule keeps "Strategy" and overrides the LLM's correct "Metrics and Targets," because A2 wins whenever it is not "Other." I set S1's hint to "Metrics and Targets" above for a clean trace, but in the real file it depends on CR Power's exact heading nesting. Not proposing a change yet, just something to check once you have real output. If it turns out to mislabel often, that is a real decision to log later.
+Why not use an LLM for heading detection, or an OCR?</t>
+  </si>
+  <si>
+    <t>DL-020</t>
+  </si>
+  <si>
+    <t>B1 : Climate relevance filter, ClimateBERT checkpoint selection</t>
+  </si>
+  <si>
+    <t>Use climatebert/distilroberta-base-climate-detector as the B1 relevance classifier, not climatebert/distilroberta-base-climate-f.</t>
+  </si>
+  <si>
+    <t>DL-018 fixes ClimateBERT as the B1 pre-filter but names no checkpoint. Two candidates exist: distilroberta-base-climate-detector, a ready-made binary classifier that labels a span climate-related or not, and distilroberta-base-climate-f, the climate-domain-adapted base language model with no classification head.</t>
+  </si>
+  <si>
+    <t>(1) climate-detector, the off-the-shelf binary climate classifier. (2) climate-f plus a new classification head fine-tuned in-house. (3) A general-domain text classifier.</t>
+  </si>
+  <si>
+    <t>The B1 task is exactly binary climate relevance, the objective climate-detector was released for, so it runs off the shelf with no training data; climate-f is a masked-language model that cannot emit a relevance label without a labelled training set the project does not have; a general classifier ignores the climate vocabulary P1 shows a domain model captures. climate-detector keeps B1 to a single pip-installable model with no bespoke training step.</t>
+  </si>
+  <si>
+    <t>climate-detector gives only a coarse climate vs non-climate judgment; finer distinctions such as net-zero versus generic climate mention are left to the B2/B3 LLM, not attempted at B1.</t>
+  </si>
+  <si>
+    <t>CORRECTED: this decision rests on P1 (Bingler et al. 2022, the project's ClimateBERT anchor) and the two Hugging Face checkpoint model cards (climate-detector = binary relevance classifier; climate-f = domain-adapted base LM with no classification head) only.</t>
+  </si>
+  <si>
+    <t>DL-021</t>
+  </si>
+  <si>
+    <t>Active Provisional</t>
+  </si>
+  <si>
+    <t>B1 : Climate relevance filter, keep threshold</t>
+  </si>
+  <si>
+    <t>Keep a segment when the model probability of the climate class is at least 0.3, rather than the default 0.5 argmax cutoff. The 0.3 value is a recall-favoring starting point to validate on the pilot and adjust if needed.</t>
+  </si>
+  <si>
+    <t>B1 is the first stage of a two-stage funnel; every segment it passes is re-judged by the B2/B3 LLM, which assigns content_type and can label non-pledge text as boilerplate. A segment B1 wrongly drops is lost permanently and never reaches Stage D.</t>
+  </si>
+  <si>
+    <t>(1) Default 0.5 argmax. (2) Recall-favoring 0.3 probability cutoff. (3) Very low 0.1 cutoff keeping almost everything.</t>
+  </si>
+  <si>
+    <t>In a funnel with a second filter a missed pledge costs more than a passed non-pledge, so B1 is tuned for recall not balanced accuracy; 0.5 optimizes the wrong objective for a first-stage sieve, while 0.1 passes so much noise it inflates B2/B3 cost for little recall gain. 0.3 keeps borderline climate text while still removing clearly non-climate segments.</t>
+  </si>
+  <si>
+    <t>A lower threshold passes more false positives into the LLM step, raising token cost and the share the LLM must label boilerplate; acceptable because LLM cost stays under USD 30 at n=200 (DL-018).</t>
+  </si>
+  <si>
+    <t>The precision/recall/threshold trade-off is the standard classification-sieve argument, recorded in the literature tracker precision-recall worked example. The 0.3 value is an engineering starting point, not a paper constant, and is flagged in code for validation against the 20-segment pilot labels.</t>
+  </si>
+  <si>
+    <t>Needs to be tested for validity. However most papers use climate bert, so genuine limitation.</t>
+  </si>
+  <si>
+    <t>DL-022</t>
+  </si>
+  <si>
+    <t>B1 : Climate relevance filter, language routing</t>
+  </si>
+  <si>
+    <t>At B1, keep only segments with detected language en and drop all others, including unknown, recording the drop rather than deleting silently.</t>
+  </si>
+  <si>
+    <t>The climate-detector checkpoint is English-only, so its scores on non-English text are not meaningful. The corpus is effectively English: across the five reviewed firms the extractable text layer is English only, with only decorative or isolated CJK characters.</t>
+  </si>
+  <si>
+    <t>(1) Route non-English segments to a separate multilingual relevance model. (2) Drop non-English segments at B1 and log the count. (3) Pass all segments through the English model regardless of language.</t>
+  </si>
+  <si>
+    <t>Option 3 yields unreliable scores on unsupported text; Option 1 adds a second model dependency for a content volume that is negligible in this corpus and unjustified for a first iteration. Option 2 matches the data, keeps a single-model pipeline, and stays auditable because dropped segments are counted and inspectable.</t>
+  </si>
+  <si>
+    <t>A genuinely climate-relevant non-English segment would be dropped; the risk is negligible here but the rule must be revisited before extending beyond English-language filings at n=200.</t>
+  </si>
+  <si>
+    <t>EDA_Log language profiles: Cathay Pacific English only; CR Power English with decorative cover Chinese; ENN Energy English only with zero CJK in the text layer; JD Logistics English only with two isolated CJK characters; Kunlun Energy English only, CJK ratio 0.001%. ClimateBERT English-only scope is per P1 and the checkpoint model card.</t>
+  </si>
+  <si>
+    <t>DL-023</t>
+  </si>
+  <si>
+    <t>B1 : Climate relevance filter, table-cell handling</t>
+  </si>
+  <si>
+    <t>Segments with source_type table_cell bypass the B1 ClimateBERT filter and pass directly to the B2/B3 LLM; the ClimateBERT threshold applies only to source_type paragraph segments.</t>
+  </si>
+  <si>
+    <t>table_cell segments are produced by the DL-019 fallback to rescue high-value Metrics and Targets content (Kunlun Net Zero Roadmap milestones, risk-table Mitigation Measures cells) from pages where extract_text() is garbled. They arrive as short fragments, not prose sentences.</t>
+  </si>
+  <si>
+    <t>(1) Apply the same paragraph threshold to table cells. (2) Bypass B1 for table cells and let the LLM judge relevance and content_type. (3) Apply a separate lower threshold to table cells.</t>
+  </si>
+  <si>
+    <t>ClimateBERT is trained on prose sentences (P1, sentence-level data), so its scores on table-cell fragments are out of distribution and unreliable, and a prose-tuned threshold risks dropping the exact Net Zero Roadmap content DL-019 was built to preserve. The B2/B3 LLM is robust to fragmentary input (DL-018) and receives a table-cell note, so it can screen relevance and assign content_type, including labelling a genuine non-pledge cell as boilerplate. Table-cell volume is small, tens of cells per affected firm, so the added LLM cost is negligible. This is the DL-018 LLM-reliance philosophy applied at B1: send variable, hard-to-rule content to the LLM rather than to a brittle threshold.</t>
+  </si>
+  <si>
+    <t>A few genuinely irrelevant table cells reach the LLM and consume tokens; preferred over silently dropping dated targets, and such cells are labelled boilerplate downstream rather than scored.</t>
+  </si>
+  <si>
+    <t>DL-019 (table-cell fallback rationale and affected Kunlun pages). P1 (Bingler et al. 2022) establishes ClimateBERT as prose-trained. DL-018 establishes the B2/B3 LLM as the component handling structured extraction under report variation.</t>
+  </si>
+  <si>
+    <t>DL-024</t>
+  </si>
+  <si>
+    <t>Decision log maintenance — citation correction</t>
+  </si>
+  <si>
+    <t>Logged correction note: on the date below, DL-018 and DL-020 were edited to remove a misattributed citation and downgrade an unverified one.</t>
+  </si>
+  <si>
+    <t>Review of the literature mastersheet found that the P9 row (Wang and Zhou, SDG-omission/greenwashing-tone paper) does not contain the 0.993 ClimateBERT F1 figure DL-018's Evidence cell had attributed to it. Separately, DL-020 cited P11 (Schimanski et al., ClimateBERT-NetZero) for specific accuracy figures and a pre-filter recommendation, but P11 is not present in the project's literature files or mastersheet, so those figures could not be verified against the source.</t>
+  </si>
+  <si>
+    <t>(1) Leave both citations as-is, since removing them weakens the stated justification for keeping ClimateBERT. (2) Correct DL-018 to drop the unverifiable P9 figure, and downgrade DL-020's P11 claims to explicitly unverified pending upload of the paper. (3) Invent a plausible substitute citation to keep the rationale looking fully sourced.</t>
+  </si>
+  <si>
+    <t>Option 3 would fabricate a reference, which the project's integrity rules explicitly forbid regardless of how minor. Option 1 leaves a false citation in an academic log meant to be examiner-auditable. Option 2 is the only choice consistent with the project's rule that decision log entries must be grounded in credible cited research, not asserted; it keeps the log honest even though it weakens the apparent evidence base for DL-018/DL-020 in the short term.</t>
+  </si>
+  <si>
+    <t>DL-018's justification for keeping ClimateBERT over a pure-LLM filter is now weaker than previously stated, resting on cost and validated relevance-classification fit (P1) rather than a specific accuracy-at-scale figure, until a correct source for that figure is found or P11 is verified and logged.</t>
+  </si>
+  <si>
+    <t>This entry itself is the audit trail: it records that the P9 mismatch and the P11 gap were identified and corrected on inspection, rather than left in the log or silently patched without a record. See corrected DL-018 and DL-020 rows above for the resulting text.</t>
+  </si>
+  <si>
+    <t>DL-025</t>
+  </si>
+  <si>
+    <t>Provisional</t>
+  </si>
+  <si>
+    <t>B2/B3 : LLM extraction, modality handling</t>
+  </si>
+  <si>
+    <t>For now the B2/B3 LLM call does not extract modality (will/shall vs ongoing vs past). Modality is left to Stage D. Flip EXTRACT_MODALITY to True in stage_b2_extract.py to move it into the same call.</t>
+  </si>
+  <si>
+    <t>Stage D needs a modality signal for scoring (Loughran-McDonald lists). It can either be pulled by the B2 LLM in the same call it already makes, or computed separately in Stage D. This is a default choice, not yet tested on our data, hence Provisional.</t>
+  </si>
+  <si>
+    <t>(1) Leave modality to Stage D. (2) Have the B2 LLM return a modality field in the same call. P10 (Xu and Suzuki 2026) extracts modality this way in its LLM call, so option 2 is known to be feasible. The two differ in a testable way: one extra JSON field and one fewer Stage D pass.</t>
+  </si>
+  <si>
+    <t>Defaulting to option 1 to keep extraction and scoring separated, so Stage D's modality logic stays rule-based and auditable rather than depending on LLM output. Revisit after the 20-segment pilot: if the LLM tags modality reliably, folding it in saves a pass.</t>
+  </si>
+  <si>
+    <t>Not validated yet, so no strong trade-off claimed. If option 1 stays, Stage D does slightly more work. If it flips later, some scoring input becomes LLM-sourced and needs the same model/run_date logging as the rest.</t>
+  </si>
+  <si>
+    <t>P10 (Xu and Suzuki 2026) for feasibility of in-call modality extraction. Loughran and McDonald 2011 modal word lists for the Stage D side. Decision to be confirmed against pilot output.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -186,10 +343,14 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +361,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E5F"/>
         <bgColor rgb="FF1F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -215,21 +382,27 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -457,14 +630,15 @@
     <col customWidth="1" min="8" max="8" width="46.0"/>
     <col customWidth="1" min="9" max="9" width="32.0"/>
     <col customWidth="1" min="10" max="10" width="46.0"/>
-    <col customWidth="1" min="11" max="25" width="8.71"/>
+    <col customWidth="1" min="11" max="11" width="72.86"/>
+    <col customWidth="1" min="12" max="25" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -493,192 +667,192 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -711,561 +885,692 @@
       <c r="J6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
+      <c r="K6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="5"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
+    <row r="9" ht="117.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="5"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
+    <row r="10" ht="94.5" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="5"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
+    <row r="11" ht="186.0" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="5"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
+    <row r="12" ht="107.25" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="5"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -2229,6 +2534,18 @@
     <row r="986" ht="15.75" customHeight="1"/>
     <row r="987" ht="15.75" customHeight="1"/>
     <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
